--- a/data/availability/projects/tatweer-misr/salt.xlsx
+++ b/data/availability/projects/tatweer-misr/salt.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -959,7 +959,6 @@
       <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -970,7 +969,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1016,7 +1015,6 @@
       <c r="G3" t="n">
         <v>75</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1027,7 +1025,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1073,7 +1071,6 @@
       <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1084,7 +1081,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1130,7 +1127,6 @@
       <c r="G5" t="n">
         <v>75</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1141,7 +1137,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1187,7 +1183,6 @@
       <c r="G6" t="n">
         <v>75</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1244,7 +1239,6 @@
       <c r="G7" t="n">
         <v>75</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1255,7 +1249,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1301,7 +1295,6 @@
       <c r="G8" t="n">
         <v>75</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1312,7 +1305,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1358,7 +1351,6 @@
       <c r="G9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1369,7 +1361,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1415,7 +1407,6 @@
       <c r="G10" t="n">
         <v>75</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1426,7 +1417,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1472,7 +1463,6 @@
       <c r="G11" t="n">
         <v>100</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1483,7 +1473,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1529,7 +1519,6 @@
       <c r="G12" t="n">
         <v>75</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1540,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1586,7 +1575,6 @@
       <c r="G13" t="n">
         <v>75</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1597,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1643,7 +1631,6 @@
       <c r="G14" t="n">
         <v>75</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1654,7 +1641,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1700,7 +1687,6 @@
       <c r="G15" t="n">
         <v>100</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1711,7 +1697,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1757,7 +1743,6 @@
       <c r="G16" t="n">
         <v>100</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1768,7 +1753,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1814,7 +1799,6 @@
       <c r="G17" t="n">
         <v>75</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1825,7 +1809,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1871,7 +1855,6 @@
       <c r="G18" t="n">
         <v>100</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1882,7 +1865,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1928,7 +1911,6 @@
       <c r="G19" t="n">
         <v>110</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1939,7 +1921,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1985,7 +1967,6 @@
       <c r="G20" t="n">
         <v>100</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1996,7 +1977,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2042,7 +2023,6 @@
       <c r="G21" t="n">
         <v>115</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2053,7 +2033,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2099,7 +2079,6 @@
       <c r="G22" t="n">
         <v>115</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2110,7 +2089,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2156,7 +2135,6 @@
       <c r="G23" t="n">
         <v>115</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2167,7 +2145,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2213,7 +2191,6 @@
       <c r="G24" t="n">
         <v>85</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2224,7 +2201,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2270,7 +2247,6 @@
       <c r="G25" t="n">
         <v>115</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2281,7 +2257,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2327,7 +2303,6 @@
       <c r="G26" t="n">
         <v>115</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2338,7 +2313,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2360,7 +2335,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2384,7 +2359,6 @@
       <c r="G27" t="n">
         <v>55</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2395,7 +2369,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2441,7 +2415,6 @@
       <c r="G28" t="n">
         <v>85</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2452,7 +2425,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2498,7 +2471,6 @@
       <c r="G29" t="n">
         <v>110</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2509,7 +2481,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2555,7 +2527,6 @@
       <c r="G30" t="n">
         <v>115</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2566,7 +2537,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2612,7 +2583,6 @@
       <c r="G31" t="n">
         <v>115</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2623,7 +2593,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2669,7 +2639,6 @@
       <c r="G32" t="n">
         <v>85</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2680,7 +2649,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2726,7 +2695,6 @@
       <c r="G33" t="n">
         <v>115</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2737,7 +2705,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2783,7 +2751,6 @@
       <c r="G34" t="n">
         <v>85</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2794,7 +2761,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2840,7 +2807,6 @@
       <c r="G35" t="n">
         <v>75</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2851,7 +2817,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2897,7 +2863,6 @@
       <c r="G36" t="n">
         <v>85</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2908,7 +2873,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2954,7 +2919,6 @@
       <c r="G37" t="n">
         <v>115</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2965,7 +2929,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3011,7 +2975,6 @@
       <c r="G38" t="n">
         <v>110</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3022,7 +2985,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3068,7 +3031,6 @@
       <c r="G39" t="n">
         <v>95</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3079,7 +3041,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3125,7 +3087,6 @@
       <c r="G40" t="n">
         <v>115</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3136,7 +3097,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3182,7 +3143,6 @@
       <c r="G41" t="n">
         <v>115</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3193,7 +3153,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3239,7 +3199,6 @@
       <c r="G42" t="n">
         <v>95</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3250,7 +3209,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3296,7 +3255,6 @@
       <c r="G43" t="n">
         <v>115</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3307,7 +3265,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3353,7 +3311,6 @@
       <c r="G44" t="n">
         <v>110</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3364,7 +3321,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3410,7 +3367,6 @@
       <c r="G45" t="n">
         <v>115</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3421,7 +3377,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3467,7 +3423,6 @@
       <c r="G46" t="n">
         <v>110</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3478,7 +3433,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3524,7 +3479,6 @@
       <c r="G47" t="n">
         <v>110</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3535,7 +3489,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3581,7 +3535,6 @@
       <c r="G48" t="n">
         <v>110</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3592,7 +3545,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3638,7 +3591,6 @@
       <c r="G49" t="n">
         <v>110</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3649,7 +3601,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3695,7 +3647,6 @@
       <c r="G50" t="n">
         <v>115</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3706,7 +3657,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3752,7 +3703,6 @@
       <c r="G51" t="n">
         <v>115</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3763,7 +3713,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3809,7 +3759,6 @@
       <c r="G52" t="n">
         <v>135</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3820,7 +3769,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3866,7 +3815,6 @@
       <c r="G53" t="n">
         <v>115</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3877,7 +3825,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3923,7 +3871,6 @@
       <c r="G54" t="n">
         <v>110</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3934,7 +3881,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3980,7 +3927,6 @@
       <c r="G55" t="n">
         <v>110</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3991,7 +3937,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4037,7 +3983,6 @@
       <c r="G56" t="n">
         <v>115</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4048,7 +3993,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4094,7 +4039,6 @@
       <c r="G57" t="n">
         <v>115</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4105,7 +4049,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4151,7 +4095,6 @@
       <c r="G58" t="n">
         <v>115</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4162,7 +4105,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4208,7 +4151,6 @@
       <c r="G59" t="n">
         <v>85</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4219,7 +4161,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4265,7 +4207,6 @@
       <c r="G60" t="n">
         <v>115</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4276,7 +4217,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4322,7 +4263,6 @@
       <c r="G61" t="n">
         <v>85</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4333,7 +4273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4379,7 +4319,6 @@
       <c r="G62" t="n">
         <v>85</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4390,7 +4329,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4436,7 +4375,6 @@
       <c r="G63" t="n">
         <v>85</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4447,7 +4385,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4469,7 +4407,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4493,7 +4431,6 @@
       <c r="G64" t="n">
         <v>55</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4504,7 +4441,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4550,7 +4487,6 @@
       <c r="G65" t="n">
         <v>110</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4561,7 +4497,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4607,7 +4543,6 @@
       <c r="G66" t="n">
         <v>115</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4618,7 +4553,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4664,7 +4599,6 @@
       <c r="G67" t="n">
         <v>115</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4675,7 +4609,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4721,7 +4655,6 @@
       <c r="G68" t="n">
         <v>115</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4732,7 +4665,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4778,7 +4711,6 @@
       <c r="G69" t="n">
         <v>115</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4789,7 +4721,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4835,7 +4767,6 @@
       <c r="G70" t="n">
         <v>85</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4846,7 +4777,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4892,7 +4823,6 @@
       <c r="G71" t="n">
         <v>85</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4903,7 +4833,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4949,7 +4879,6 @@
       <c r="G72" t="n">
         <v>115</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4960,7 +4889,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5006,7 +4935,6 @@
       <c r="G73" t="n">
         <v>85</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5017,7 +4945,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5063,7 +4991,6 @@
       <c r="G74" t="n">
         <v>85</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5074,7 +5001,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5120,7 +5047,6 @@
       <c r="G75" t="n">
         <v>115</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5131,7 +5057,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5177,7 +5103,6 @@
       <c r="G76" t="n">
         <v>135</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5188,7 +5113,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5234,7 +5159,6 @@
       <c r="G77" t="n">
         <v>85</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5245,7 +5169,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5291,7 +5215,6 @@
       <c r="G78" t="n">
         <v>85</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5302,7 +5225,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5348,7 +5271,6 @@
       <c r="G79" t="n">
         <v>135</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5359,7 +5281,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5405,7 +5327,6 @@
       <c r="G80" t="n">
         <v>135</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5416,7 +5337,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5462,7 +5383,6 @@
       <c r="G81" t="n">
         <v>110</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5473,7 +5393,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5519,7 +5439,6 @@
       <c r="G82" t="n">
         <v>110</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5530,7 +5449,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5576,7 +5495,6 @@
       <c r="G83" t="n">
         <v>135</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5587,7 +5505,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5633,7 +5551,6 @@
       <c r="G84" t="n">
         <v>100</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5644,7 +5561,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5690,7 +5607,6 @@
       <c r="G85" t="n">
         <v>115</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5701,7 +5617,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5747,7 +5663,6 @@
       <c r="G86" t="n">
         <v>115</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5758,7 +5673,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5804,7 +5719,6 @@
       <c r="G87" t="n">
         <v>115</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5815,7 +5729,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5861,7 +5775,6 @@
       <c r="G88" t="n">
         <v>115</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5872,7 +5785,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5918,7 +5831,6 @@
       <c r="G89" t="n">
         <v>115</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5929,7 +5841,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5975,7 +5887,6 @@
       <c r="G90" t="n">
         <v>85</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5986,7 +5897,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6032,7 +5943,6 @@
       <c r="G91" t="n">
         <v>85</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6043,7 +5953,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6089,7 +5999,6 @@
       <c r="G92" t="n">
         <v>115</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6100,7 +6009,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6146,7 +6055,6 @@
       <c r="G93" t="n">
         <v>115</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6157,7 +6065,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6179,7 +6087,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6203,7 +6111,6 @@
       <c r="G94" t="n">
         <v>45</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6214,7 +6121,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6260,7 +6167,6 @@
       <c r="G95" t="n">
         <v>85</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6271,7 +6177,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6317,7 +6223,6 @@
       <c r="G96" t="n">
         <v>85</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6328,7 +6233,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6374,7 +6279,6 @@
       <c r="G97" t="n">
         <v>115</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6385,7 +6289,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6431,7 +6335,6 @@
       <c r="G98" t="n">
         <v>135</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6442,7 +6345,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6488,7 +6391,6 @@
       <c r="G99" t="n">
         <v>135</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6499,7 +6401,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6545,7 +6447,6 @@
       <c r="G100" t="n">
         <v>135</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6556,7 +6457,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6602,7 +6503,6 @@
       <c r="G101" t="n">
         <v>110</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6613,7 +6513,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6659,7 +6559,6 @@
       <c r="G102" t="n">
         <v>110</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6670,7 +6569,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6716,7 +6615,6 @@
       <c r="G103" t="n">
         <v>115</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6727,7 +6625,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6773,7 +6671,6 @@
       <c r="G104" t="n">
         <v>115</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6784,7 +6681,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6830,7 +6727,6 @@
       <c r="G105" t="n">
         <v>100</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6841,7 +6737,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6887,7 +6783,6 @@
       <c r="G106" t="n">
         <v>115</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6898,7 +6793,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6944,7 +6839,6 @@
       <c r="G107" t="n">
         <v>115</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6955,7 +6849,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7001,7 +6895,6 @@
       <c r="G108" t="n">
         <v>100</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7012,7 +6905,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7058,7 +6951,6 @@
       <c r="G109" t="n">
         <v>115</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7069,7 +6961,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7115,7 +7007,6 @@
       <c r="G110" t="n">
         <v>115</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7126,7 +7017,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7172,7 +7063,6 @@
       <c r="G111" t="n">
         <v>100</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7183,7 +7073,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7229,7 +7119,6 @@
       <c r="G112" t="n">
         <v>75</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7240,7 +7129,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7286,7 +7175,6 @@
       <c r="G113" t="n">
         <v>100</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7297,7 +7185,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7343,7 +7231,6 @@
       <c r="G114" t="n">
         <v>115</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7354,7 +7241,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7400,7 +7287,6 @@
       <c r="G115" t="n">
         <v>115</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7411,7 +7297,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7457,7 +7343,6 @@
       <c r="G116" t="n">
         <v>115</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7468,7 +7353,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7514,7 +7399,6 @@
       <c r="G117" t="n">
         <v>75</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7525,7 +7409,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7571,7 +7455,6 @@
       <c r="G118" t="n">
         <v>115</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7582,7 +7465,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7628,7 +7511,6 @@
       <c r="G119" t="n">
         <v>100</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7639,7 +7521,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7685,7 +7567,6 @@
       <c r="G120" t="n">
         <v>75</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7696,7 +7577,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7742,7 +7623,6 @@
       <c r="G121" t="n">
         <v>115</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7753,7 +7633,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7799,7 +7679,6 @@
       <c r="G122" t="n">
         <v>110</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7810,7 +7689,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7856,7 +7735,6 @@
       <c r="G123" t="n">
         <v>110</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7867,7 +7745,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7913,7 +7791,6 @@
       <c r="G124" t="n">
         <v>115</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7924,7 +7801,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7970,7 +7847,6 @@
       <c r="G125" t="n">
         <v>100</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7981,7 +7857,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8027,7 +7903,6 @@
       <c r="G126" t="n">
         <v>115</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8038,7 +7913,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8084,7 +7959,6 @@
       <c r="G127" t="n">
         <v>115</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8095,7 +7969,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8141,7 +8015,6 @@
       <c r="G128" t="n">
         <v>115</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8152,7 +8025,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8198,7 +8071,6 @@
       <c r="G129" t="n">
         <v>100</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8209,7 +8081,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8255,7 +8127,6 @@
       <c r="G130" t="n">
         <v>115</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8266,7 +8137,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8312,7 +8183,6 @@
       <c r="G131" t="n">
         <v>110</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8323,7 +8193,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8369,7 +8239,6 @@
       <c r="G132" t="n">
         <v>110</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8380,7 +8249,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8426,7 +8295,6 @@
       <c r="G133" t="n">
         <v>110</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8437,7 +8305,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8483,7 +8351,6 @@
       <c r="G134" t="n">
         <v>95</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8494,7 +8361,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8540,7 +8407,6 @@
       <c r="G135" t="n">
         <v>100</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8551,7 +8417,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8597,7 +8463,6 @@
       <c r="G136" t="n">
         <v>95</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8608,7 +8473,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8654,7 +8519,6 @@
       <c r="G137" t="n">
         <v>100</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8665,7 +8529,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8711,7 +8575,6 @@
       <c r="G138" t="n">
         <v>65</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8722,7 +8585,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8768,7 +8631,6 @@
       <c r="G139" t="n">
         <v>100</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8779,7 +8641,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8825,7 +8687,6 @@
       <c r="G140" t="n">
         <v>75</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8836,7 +8697,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8882,7 +8743,6 @@
       <c r="G141" t="n">
         <v>65</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8893,7 +8753,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8939,7 +8799,6 @@
       <c r="G142" t="n">
         <v>100</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8950,7 +8809,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8996,7 +8855,6 @@
       <c r="G143" t="n">
         <v>75</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9007,7 +8865,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9053,7 +8911,6 @@
       <c r="G144" t="n">
         <v>100</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9064,7 +8921,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9110,7 +8967,6 @@
       <c r="G145" t="n">
         <v>75</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9121,7 +8977,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9167,7 +9023,6 @@
       <c r="G146" t="n">
         <v>100</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9178,7 +9033,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9224,7 +9079,6 @@
       <c r="G147" t="n">
         <v>100</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9235,7 +9089,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9281,7 +9135,6 @@
       <c r="G148" t="n">
         <v>65</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9292,7 +9145,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9338,7 +9191,6 @@
       <c r="G149" t="n">
         <v>115</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9349,7 +9201,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9395,7 +9247,6 @@
       <c r="G150" t="n">
         <v>100</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9406,7 +9257,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9452,7 +9303,6 @@
       <c r="G151" t="n">
         <v>100</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9463,7 +9313,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9509,7 +9359,6 @@
       <c r="G152" t="n">
         <v>65</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9520,7 +9369,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9566,7 +9415,6 @@
       <c r="G153" t="n">
         <v>65</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9577,7 +9425,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9623,7 +9471,6 @@
       <c r="G154" t="n">
         <v>115</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9634,7 +9481,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9680,7 +9527,6 @@
       <c r="G155" t="n">
         <v>100</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9691,7 +9537,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9737,7 +9583,6 @@
       <c r="G156" t="n">
         <v>100</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9748,7 +9593,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9794,7 +9639,6 @@
       <c r="G157" t="n">
         <v>75</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9805,7 +9649,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9851,7 +9695,6 @@
       <c r="G158" t="n">
         <v>65</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9862,7 +9705,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9908,7 +9751,6 @@
       <c r="G159" t="n">
         <v>115</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9919,7 +9761,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9965,7 +9807,6 @@
       <c r="G160" t="n">
         <v>100</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9976,7 +9817,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10022,7 +9863,6 @@
       <c r="G161" t="n">
         <v>115</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10033,7 +9873,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10079,7 +9919,6 @@
       <c r="G162" t="n">
         <v>75</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10090,7 +9929,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10136,7 +9975,6 @@
       <c r="G163" t="n">
         <v>65</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10147,7 +9985,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10193,7 +10031,6 @@
       <c r="G164" t="n">
         <v>115</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10204,7 +10041,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10250,7 +10087,6 @@
       <c r="G165" t="n">
         <v>100</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10261,7 +10097,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10307,7 +10143,6 @@
       <c r="G166" t="n">
         <v>75</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10318,7 +10153,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10364,7 +10199,6 @@
       <c r="G167" t="n">
         <v>65</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10375,7 +10209,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10421,7 +10255,6 @@
       <c r="G168" t="n">
         <v>100</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10432,7 +10265,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10478,7 +10311,6 @@
       <c r="G169" t="n">
         <v>100</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10489,7 +10321,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10535,7 +10367,6 @@
       <c r="G170" t="n">
         <v>115</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10546,7 +10377,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10592,7 +10423,6 @@
       <c r="G171" t="n">
         <v>110</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10603,7 +10433,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10649,7 +10479,6 @@
       <c r="G172" t="n">
         <v>110</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10660,7 +10489,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10706,7 +10535,6 @@
       <c r="G173" t="n">
         <v>100</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10717,7 +10545,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10763,7 +10591,6 @@
       <c r="G174" t="n">
         <v>100</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10774,7 +10601,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10820,7 +10647,6 @@
       <c r="G175" t="n">
         <v>115</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10831,7 +10657,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10877,7 +10703,6 @@
       <c r="G176" t="n">
         <v>65</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10888,7 +10713,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10934,7 +10759,6 @@
       <c r="G177" t="n">
         <v>75</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10945,7 +10769,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10991,7 +10815,6 @@
       <c r="G178" t="n">
         <v>100</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11002,7 +10825,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11048,7 +10871,6 @@
       <c r="G179" t="n">
         <v>115</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11059,7 +10881,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11105,7 +10927,6 @@
       <c r="G180" t="n">
         <v>95</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11116,7 +10937,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11162,7 +10983,6 @@
       <c r="G181" t="n">
         <v>100</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11173,7 +10993,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11219,7 +11039,6 @@
       <c r="G182" t="n">
         <v>95</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11230,7 +11049,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11276,7 +11095,6 @@
       <c r="G183" t="n">
         <v>100</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11287,7 +11105,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11333,7 +11151,6 @@
       <c r="G184" t="n">
         <v>75</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11344,7 +11161,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11390,7 +11207,6 @@
       <c r="G185" t="n">
         <v>100</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11401,7 +11217,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11447,7 +11263,6 @@
       <c r="G186" t="n">
         <v>100</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11458,7 +11273,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11504,7 +11319,6 @@
       <c r="G187" t="n">
         <v>75</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11515,7 +11329,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11561,7 +11375,6 @@
       <c r="G188" t="n">
         <v>95</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11572,7 +11385,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11618,7 +11431,6 @@
       <c r="G189" t="n">
         <v>100</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11629,7 +11441,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11675,7 +11487,6 @@
       <c r="G190" t="n">
         <v>110</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11686,7 +11497,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11732,7 +11543,6 @@
       <c r="G191" t="n">
         <v>75</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11743,7 +11553,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11789,7 +11599,6 @@
       <c r="G192" t="n">
         <v>110</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11800,7 +11609,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11846,7 +11655,6 @@
       <c r="G193" t="n">
         <v>95</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11857,7 +11665,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11903,7 +11711,6 @@
       <c r="G194" t="n">
         <v>100</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11914,7 +11721,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11960,7 +11767,6 @@
       <c r="G195" t="n">
         <v>95</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11971,7 +11777,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12017,7 +11823,6 @@
       <c r="G196" t="n">
         <v>95</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12028,7 +11833,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12074,7 +11879,6 @@
       <c r="G197" t="n">
         <v>110</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12085,7 +11889,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12131,7 +11935,6 @@
       <c r="G198" t="n">
         <v>95</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12142,7 +11945,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12188,7 +11991,6 @@
       <c r="G199" t="n">
         <v>100</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12199,7 +12001,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12245,7 +12047,6 @@
       <c r="G200" t="n">
         <v>65</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12256,7 +12057,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12302,7 +12103,6 @@
       <c r="G201" t="n">
         <v>75</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12313,7 +12113,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12359,7 +12159,6 @@
       <c r="G202" t="n">
         <v>110</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12370,7 +12169,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12416,7 +12215,6 @@
       <c r="G203" t="n">
         <v>65</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12427,7 +12225,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12473,7 +12271,6 @@
       <c r="G204" t="n">
         <v>100</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12484,7 +12281,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12530,7 +12327,6 @@
       <c r="G205" t="n">
         <v>95</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12541,7 +12337,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12587,7 +12383,6 @@
       <c r="G206" t="n">
         <v>95</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12598,7 +12393,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12644,7 +12439,6 @@
       <c r="G207" t="n">
         <v>110</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12655,7 +12449,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12701,7 +12495,6 @@
       <c r="G208" t="n">
         <v>110</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12712,7 +12505,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12758,7 +12551,6 @@
       <c r="G209" t="n">
         <v>95</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12769,7 +12561,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12815,7 +12607,6 @@
       <c r="G210" t="n">
         <v>100</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12826,7 +12617,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12872,7 +12663,6 @@
       <c r="G211" t="n">
         <v>95</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12883,7 +12673,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12929,7 +12719,6 @@
       <c r="G212" t="n">
         <v>65</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12940,7 +12729,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12986,7 +12775,6 @@
       <c r="G213" t="n">
         <v>110</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12997,7 +12785,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13043,7 +12831,6 @@
       <c r="G214" t="n">
         <v>110</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13054,7 +12841,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13100,7 +12887,6 @@
       <c r="G215" t="n">
         <v>75</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13111,7 +12897,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13157,7 +12943,6 @@
       <c r="G216" t="n">
         <v>65</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13168,7 +12953,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13214,7 +12999,6 @@
       <c r="G217" t="n">
         <v>95</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13225,7 +13009,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -13271,7 +13055,6 @@
       <c r="G218" t="n">
         <v>65</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13282,7 +13065,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13328,7 +13111,6 @@
       <c r="G219" t="n">
         <v>95</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13339,7 +13121,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13385,7 +13167,6 @@
       <c r="G220" t="n">
         <v>75</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13396,7 +13177,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13442,7 +13223,6 @@
       <c r="G221" t="n">
         <v>95</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13453,7 +13233,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13499,7 +13279,6 @@
       <c r="G222" t="n">
         <v>100</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13510,7 +13289,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13556,7 +13335,6 @@
       <c r="G223" t="n">
         <v>95</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13567,7 +13345,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13613,7 +13391,6 @@
       <c r="G224" t="n">
         <v>115</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13624,7 +13401,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13670,7 +13447,6 @@
       <c r="G225" t="n">
         <v>110</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13681,7 +13457,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13727,7 +13503,6 @@
       <c r="G226" t="n">
         <v>115</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13738,7 +13513,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13784,7 +13559,6 @@
       <c r="G227" t="n">
         <v>75</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13795,7 +13569,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13841,7 +13615,6 @@
       <c r="G228" t="n">
         <v>115</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13852,7 +13625,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13898,7 +13671,6 @@
       <c r="G229" t="n">
         <v>95</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13909,7 +13681,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13955,7 +13727,6 @@
       <c r="G230" t="n">
         <v>65</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13966,7 +13737,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14012,7 +13783,6 @@
       <c r="G231" t="n">
         <v>100</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14023,7 +13793,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14069,7 +13839,6 @@
       <c r="G232" t="n">
         <v>100</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14080,7 +13849,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -14126,7 +13895,6 @@
       <c r="G233" t="n">
         <v>85</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14137,7 +13905,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -14183,7 +13951,6 @@
       <c r="G234" t="n">
         <v>100</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14194,7 +13961,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -14240,7 +14007,6 @@
       <c r="G235" t="n">
         <v>85</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14251,7 +14017,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14297,7 +14063,6 @@
       <c r="G236" t="n">
         <v>75</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14308,7 +14073,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14354,7 +14119,6 @@
       <c r="G237" t="n">
         <v>65</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14365,7 +14129,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14411,7 +14175,6 @@
       <c r="G238" t="n">
         <v>100</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14422,7 +14185,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14468,7 +14231,6 @@
       <c r="G239" t="n">
         <v>115</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14479,7 +14241,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14525,7 +14287,6 @@
       <c r="G240" t="n">
         <v>115</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14536,7 +14297,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14582,7 +14343,6 @@
       <c r="G241" t="n">
         <v>100</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14593,7 +14353,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14639,7 +14399,6 @@
       <c r="G242" t="n">
         <v>100</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14650,7 +14409,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14696,7 +14455,6 @@
       <c r="G243" t="n">
         <v>85</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14707,7 +14465,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14753,7 +14511,6 @@
       <c r="G244" t="n">
         <v>65</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14764,7 +14521,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14810,7 +14567,6 @@
       <c r="G245" t="n">
         <v>65</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14821,7 +14577,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14867,7 +14623,6 @@
       <c r="G246" t="n">
         <v>135</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14878,7 +14633,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14924,7 +14679,6 @@
       <c r="G247" t="n">
         <v>100</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14935,7 +14689,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14981,7 +14735,6 @@
       <c r="G248" t="n">
         <v>100</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14992,7 +14745,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -15038,7 +14791,6 @@
       <c r="G249" t="n">
         <v>65</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15049,7 +14801,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -15095,7 +14847,6 @@
       <c r="G250" t="n">
         <v>75</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15106,7 +14857,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -15152,7 +14903,6 @@
       <c r="G251" t="n">
         <v>100</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15163,7 +14913,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -15209,7 +14959,6 @@
       <c r="G252" t="n">
         <v>135</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15220,7 +14969,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -15266,7 +15015,6 @@
       <c r="G253" t="n">
         <v>75</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15277,7 +15025,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15323,7 +15071,6 @@
       <c r="G254" t="n">
         <v>100</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15334,7 +15081,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -15380,7 +15127,6 @@
       <c r="G255" t="n">
         <v>110</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15391,7 +15137,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -15437,7 +15183,6 @@
       <c r="G256" t="n">
         <v>110</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15448,7 +15193,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -15494,7 +15239,6 @@
       <c r="G257" t="n">
         <v>75</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15505,7 +15249,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -15551,7 +15295,6 @@
       <c r="G258" t="n">
         <v>115</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15562,7 +15305,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15608,7 +15351,6 @@
       <c r="G259" t="n">
         <v>100</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15619,7 +15361,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15665,7 +15407,6 @@
       <c r="G260" t="n">
         <v>115</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15676,7 +15417,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15722,7 +15463,6 @@
       <c r="G261" t="n">
         <v>115</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15733,7 +15473,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15779,7 +15519,6 @@
       <c r="G262" t="n">
         <v>115</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15790,7 +15529,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15836,7 +15575,6 @@
       <c r="G263" t="n">
         <v>75</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15847,7 +15585,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15893,7 +15631,6 @@
       <c r="G264" t="n">
         <v>115</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15904,7 +15641,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15950,7 +15687,6 @@
       <c r="G265" t="n">
         <v>65</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15961,7 +15697,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -16007,7 +15743,6 @@
       <c r="G266" t="n">
         <v>135</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16018,7 +15753,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -16064,7 +15799,6 @@
       <c r="G267" t="n">
         <v>115</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16075,7 +15809,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -16121,7 +15855,6 @@
       <c r="G268" t="n">
         <v>115</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16132,7 +15865,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16178,7 +15911,6 @@
       <c r="G269" t="n">
         <v>85</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16189,7 +15921,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -16235,7 +15967,6 @@
       <c r="G270" t="n">
         <v>115</v>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16246,7 +15977,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16292,7 +16023,6 @@
       <c r="G271" t="n">
         <v>85</v>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16303,7 +16033,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -16349,7 +16079,6 @@
       <c r="G272" t="n">
         <v>85</v>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16360,7 +16089,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16406,7 +16135,6 @@
       <c r="G273" t="n">
         <v>75</v>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16417,7 +16145,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -16463,7 +16191,6 @@
       <c r="G274" t="n">
         <v>85</v>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16474,7 +16201,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -16520,7 +16247,6 @@
       <c r="G275" t="n">
         <v>100</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16531,7 +16257,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -16577,7 +16303,6 @@
       <c r="G276" t="n">
         <v>75</v>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16588,7 +16313,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16634,7 +16359,6 @@
       <c r="G277" t="n">
         <v>110</v>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16645,7 +16369,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -16691,7 +16415,6 @@
       <c r="G278" t="n">
         <v>100</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16702,7 +16425,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -16748,7 +16471,6 @@
       <c r="G279" t="n">
         <v>100</v>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16759,7 +16481,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16805,7 +16527,6 @@
       <c r="G280" t="n">
         <v>115</v>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16816,7 +16537,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16862,7 +16583,6 @@
       <c r="G281" t="n">
         <v>115</v>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16873,7 +16593,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -16919,7 +16639,6 @@
       <c r="G282" t="n">
         <v>75</v>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16930,7 +16649,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -16976,7 +16695,6 @@
       <c r="G283" t="n">
         <v>115</v>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16987,7 +16705,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -17033,7 +16751,6 @@
       <c r="G284" t="n">
         <v>100</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17044,7 +16761,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -17090,7 +16807,6 @@
       <c r="G285" t="n">
         <v>115</v>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17101,7 +16817,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -17147,7 +16863,6 @@
       <c r="G286" t="n">
         <v>85</v>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17158,7 +16873,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -17204,7 +16919,6 @@
       <c r="G287" t="n">
         <v>75</v>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17215,7 +16929,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -17261,7 +16975,6 @@
       <c r="G288" t="n">
         <v>115</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17272,7 +16985,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17318,7 +17031,6 @@
       <c r="G289" t="n">
         <v>115</v>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17329,7 +17041,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -17375,7 +17087,6 @@
       <c r="G290" t="n">
         <v>85</v>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17386,7 +17097,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -17432,7 +17143,6 @@
       <c r="G291" t="n">
         <v>75</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17443,7 +17153,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17489,7 +17199,6 @@
       <c r="G292" t="n">
         <v>85</v>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17500,7 +17209,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -17546,7 +17255,6 @@
       <c r="G293" t="n">
         <v>95</v>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17557,7 +17265,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -17603,7 +17311,6 @@
       <c r="G294" t="n">
         <v>135</v>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17614,7 +17321,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -17660,7 +17367,6 @@
       <c r="G295" t="n">
         <v>110</v>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17671,7 +17377,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -17717,7 +17423,6 @@
       <c r="G296" t="n">
         <v>110</v>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17728,7 +17433,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -17774,7 +17479,6 @@
       <c r="G297" t="n">
         <v>95</v>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17785,7 +17489,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -17831,7 +17535,6 @@
       <c r="G298" t="n">
         <v>110</v>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17842,7 +17545,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -17888,7 +17591,6 @@
       <c r="G299" t="n">
         <v>110</v>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17899,7 +17601,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -17945,7 +17647,6 @@
       <c r="G300" t="n">
         <v>110</v>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17956,7 +17657,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -18002,7 +17703,6 @@
       <c r="G301" t="n">
         <v>110</v>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18013,7 +17713,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -18059,7 +17759,6 @@
       <c r="G302" t="n">
         <v>115</v>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18070,7 +17769,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -18116,7 +17815,6 @@
       <c r="G303" t="n">
         <v>115</v>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18127,7 +17825,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -18173,7 +17871,6 @@
       <c r="G304" t="n">
         <v>110</v>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18184,7 +17881,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -18230,7 +17927,6 @@
       <c r="G305" t="n">
         <v>115</v>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18241,7 +17937,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -18287,7 +17983,6 @@
       <c r="G306" t="n">
         <v>115</v>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18298,7 +17993,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -18344,7 +18039,6 @@
       <c r="G307" t="n">
         <v>95</v>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18355,7 +18049,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -18401,7 +18095,6 @@
       <c r="G308" t="n">
         <v>85</v>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18412,7 +18105,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -18458,7 +18151,6 @@
       <c r="G309" t="n">
         <v>110</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18469,7 +18161,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -18515,7 +18207,6 @@
       <c r="G310" t="n">
         <v>110</v>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18526,7 +18217,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -18572,7 +18263,6 @@
       <c r="G311" t="n">
         <v>95</v>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18583,7 +18273,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -18629,7 +18319,6 @@
       <c r="G312" t="n">
         <v>115</v>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18640,7 +18329,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -18686,7 +18375,6 @@
       <c r="G313" t="n">
         <v>85</v>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18697,7 +18385,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -18743,7 +18431,6 @@
       <c r="G314" t="n">
         <v>110</v>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18754,7 +18441,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -18800,7 +18487,6 @@
       <c r="G315" t="n">
         <v>110</v>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18811,7 +18497,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -18833,7 +18519,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18857,7 +18543,6 @@
       <c r="G316" t="n">
         <v>145</v>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18868,7 +18553,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -18914,7 +18599,6 @@
       <c r="G317" t="n">
         <v>115</v>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18925,7 +18609,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -18971,7 +18655,6 @@
       <c r="G318" t="n">
         <v>115</v>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18982,7 +18665,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -19028,7 +18711,6 @@
       <c r="G319" t="n">
         <v>100</v>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19039,7 +18721,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -19085,7 +18767,6 @@
       <c r="G320" t="n">
         <v>100</v>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19096,7 +18777,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -19142,7 +18823,6 @@
       <c r="G321" t="n">
         <v>115</v>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19153,7 +18833,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -19199,7 +18879,6 @@
       <c r="G322" t="n">
         <v>75</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19210,7 +18889,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -19256,7 +18935,6 @@
       <c r="G323" t="n">
         <v>75</v>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19267,7 +18945,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -19313,7 +18991,6 @@
       <c r="G324" t="n">
         <v>100</v>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19324,7 +19001,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -19370,7 +19047,6 @@
       <c r="G325" t="n">
         <v>110</v>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19381,7 +19057,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -19427,7 +19103,6 @@
       <c r="G326" t="n">
         <v>110</v>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19438,7 +19113,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -19484,7 +19159,6 @@
       <c r="G327" t="n">
         <v>110</v>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19495,7 +19169,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -19541,7 +19215,6 @@
       <c r="G328" t="n">
         <v>110</v>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19552,7 +19225,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -19598,7 +19271,6 @@
       <c r="G329" t="n">
         <v>110</v>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19609,7 +19281,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -19655,7 +19327,6 @@
       <c r="G330" t="n">
         <v>110</v>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19666,7 +19337,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -19712,7 +19383,6 @@
       <c r="G331" t="n">
         <v>110</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19723,7 +19393,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -19769,7 +19439,6 @@
       <c r="G332" t="n">
         <v>110</v>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19780,7 +19449,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -19826,7 +19495,6 @@
       <c r="G333" t="n">
         <v>95</v>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19837,7 +19505,7 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -19883,7 +19551,6 @@
       <c r="G334" t="n">
         <v>95</v>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19894,7 +19561,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -19940,7 +19607,6 @@
       <c r="G335" t="n">
         <v>95</v>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19951,7 +19617,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -19997,7 +19663,6 @@
       <c r="G336" t="n">
         <v>110</v>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20008,7 +19673,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -20054,7 +19719,6 @@
       <c r="G337" t="n">
         <v>110</v>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20065,7 +19729,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -20111,7 +19775,6 @@
       <c r="G338" t="n">
         <v>120</v>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20122,7 +19785,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -20168,7 +19831,6 @@
       <c r="G339" t="n">
         <v>95</v>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20179,7 +19841,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -20225,7 +19887,6 @@
       <c r="G340" t="n">
         <v>110</v>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20236,7 +19897,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -20258,7 +19919,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -20282,7 +19943,6 @@
       <c r="G341" t="n">
         <v>250</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20293,7 +19953,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -20315,7 +19975,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -20339,7 +19999,6 @@
       <c r="G342" t="n">
         <v>250</v>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20350,7 +20009,7 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -20372,7 +20031,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -20396,7 +20055,6 @@
       <c r="G343" t="n">
         <v>180</v>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20407,7 +20065,7 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -20429,7 +20087,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -20453,7 +20111,6 @@
       <c r="G344" t="n">
         <v>180</v>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20464,7 +20121,7 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -20486,7 +20143,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -20510,7 +20167,6 @@
       <c r="G345" t="n">
         <v>180</v>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20521,7 +20177,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -20543,7 +20199,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20567,7 +20223,6 @@
       <c r="G346" t="n">
         <v>150</v>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20578,7 +20233,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -20624,7 +20279,6 @@
       <c r="G347" t="n">
         <v>95</v>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20635,7 +20289,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -20681,7 +20335,6 @@
       <c r="G348" t="n">
         <v>110</v>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20692,7 +20345,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -20714,7 +20367,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20738,7 +20391,6 @@
       <c r="G349" t="n">
         <v>150</v>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20749,7 +20401,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -20795,7 +20447,6 @@
       <c r="G350" t="n">
         <v>110</v>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20806,7 +20457,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -20852,7 +20503,6 @@
       <c r="G351" t="n">
         <v>95</v>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20863,7 +20513,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -20909,7 +20559,6 @@
       <c r="G352" t="n">
         <v>95</v>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20920,7 +20569,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -20966,7 +20615,6 @@
       <c r="G353" t="n">
         <v>95</v>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20977,7 +20625,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -21023,7 +20671,6 @@
       <c r="G354" t="n">
         <v>110</v>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21034,7 +20681,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -21080,7 +20727,6 @@
       <c r="G355" t="n">
         <v>95</v>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21091,7 +20737,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -21137,7 +20783,6 @@
       <c r="G356" t="n">
         <v>110</v>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21148,7 +20793,7 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -21194,7 +20839,6 @@
       <c r="G357" t="n">
         <v>110</v>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21205,7 +20849,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -21251,7 +20895,6 @@
       <c r="G358" t="n">
         <v>95</v>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21262,7 +20905,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -21308,7 +20951,6 @@
       <c r="G359" t="n">
         <v>110</v>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21319,7 +20961,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -21365,7 +21007,6 @@
       <c r="G360" t="n">
         <v>110</v>
       </c>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21376,7 +21017,7 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -21422,7 +21063,6 @@
       <c r="G361" t="n">
         <v>110</v>
       </c>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21433,7 +21073,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -21479,7 +21119,6 @@
       <c r="G362" t="n">
         <v>110</v>
       </c>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21490,7 +21129,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -21536,7 +21175,6 @@
       <c r="G363" t="n">
         <v>110</v>
       </c>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21547,7 +21185,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -21569,7 +21207,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -21593,7 +21231,6 @@
       <c r="G364" t="n">
         <v>290</v>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21604,7 +21241,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -21626,7 +21263,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -21650,7 +21287,6 @@
       <c r="G365" t="n">
         <v>220</v>
       </c>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21661,7 +21297,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -21683,7 +21319,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -21707,7 +21343,6 @@
       <c r="G366" t="n">
         <v>220</v>
       </c>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21718,7 +21353,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -21764,7 +21399,6 @@
       <c r="G367" t="n">
         <v>105</v>
       </c>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21775,7 +21409,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -21821,7 +21455,6 @@
       <c r="G368" t="n">
         <v>95</v>
       </c>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21832,7 +21465,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -21878,7 +21511,6 @@
       <c r="G369" t="n">
         <v>80</v>
       </c>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21889,7 +21521,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -21935,7 +21567,6 @@
       <c r="G370" t="n">
         <v>115</v>
       </c>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21946,7 +21577,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -21992,7 +21623,6 @@
       <c r="G371" t="n">
         <v>105</v>
       </c>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22003,7 +21633,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -22049,7 +21679,6 @@
       <c r="G372" t="n">
         <v>105</v>
       </c>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22060,7 +21689,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -22106,7 +21735,6 @@
       <c r="G373" t="n">
         <v>115</v>
       </c>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22117,7 +21745,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -22163,7 +21791,6 @@
       <c r="G374" t="n">
         <v>95</v>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22174,7 +21801,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -22220,7 +21847,6 @@
       <c r="G375" t="n">
         <v>95</v>
       </c>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22231,7 +21857,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -22277,7 +21903,6 @@
       <c r="G376" t="n">
         <v>95</v>
       </c>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22288,7 +21913,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -22334,7 +21959,6 @@
       <c r="G377" t="n">
         <v>110</v>
       </c>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22345,7 +21969,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -22391,7 +22015,6 @@
       <c r="G378" t="n">
         <v>95</v>
       </c>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22402,7 +22025,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -22448,7 +22071,6 @@
       <c r="G379" t="n">
         <v>110</v>
       </c>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22459,7 +22081,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -22505,7 +22127,6 @@
       <c r="G380" t="n">
         <v>110</v>
       </c>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22516,7 +22137,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -22562,7 +22183,6 @@
       <c r="G381" t="n">
         <v>110</v>
       </c>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22573,7 +22193,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -22619,7 +22239,6 @@
       <c r="G382" t="n">
         <v>110</v>
       </c>
-      <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22630,7 +22249,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -22676,7 +22295,6 @@
       <c r="G383" t="n">
         <v>110</v>
       </c>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22687,7 +22305,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -22733,7 +22351,6 @@
       <c r="G384" t="n">
         <v>110</v>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22744,7 +22361,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -22790,7 +22407,6 @@
       <c r="G385" t="n">
         <v>110</v>
       </c>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22801,7 +22417,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -22847,7 +22463,6 @@
       <c r="G386" t="n">
         <v>110</v>
       </c>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22858,7 +22473,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -22904,7 +22519,6 @@
       <c r="G387" t="n">
         <v>110</v>
       </c>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22915,7 +22529,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -22961,7 +22575,6 @@
       <c r="G388" t="n">
         <v>95</v>
       </c>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22972,7 +22585,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -23018,7 +22631,6 @@
       <c r="G389" t="n">
         <v>110</v>
       </c>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23029,7 +22641,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -23075,7 +22687,6 @@
       <c r="G390" t="n">
         <v>110</v>
       </c>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23086,7 +22697,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -23132,7 +22743,6 @@
       <c r="G391" t="n">
         <v>110</v>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23143,7 +22753,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -23189,7 +22799,6 @@
       <c r="G392" t="n">
         <v>110</v>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23200,7 +22809,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -23246,7 +22855,6 @@
       <c r="G393" t="n">
         <v>110</v>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23257,7 +22865,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -23303,7 +22911,6 @@
       <c r="G394" t="n">
         <v>95</v>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23314,7 +22921,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -23360,7 +22967,6 @@
       <c r="G395" t="n">
         <v>110</v>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23371,7 +22977,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -23417,7 +23023,6 @@
       <c r="G396" t="n">
         <v>110</v>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23428,7 +23033,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -23474,7 +23079,6 @@
       <c r="G397" t="n">
         <v>95</v>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23485,7 +23089,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -23531,7 +23135,6 @@
       <c r="G398" t="n">
         <v>110</v>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23542,7 +23145,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -23588,7 +23191,6 @@
       <c r="G399" t="n">
         <v>110</v>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23599,7 +23201,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -23645,7 +23247,6 @@
       <c r="G400" t="n">
         <v>110</v>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23656,7 +23257,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -23702,7 +23303,6 @@
       <c r="G401" t="n">
         <v>110</v>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23713,7 +23313,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -23759,7 +23359,6 @@
       <c r="G402" t="n">
         <v>95</v>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23770,7 +23369,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -23816,7 +23415,6 @@
       <c r="G403" t="n">
         <v>110</v>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23827,7 +23425,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -23873,7 +23471,6 @@
       <c r="G404" t="n">
         <v>110</v>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23884,7 +23481,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -23930,7 +23527,6 @@
       <c r="G405" t="n">
         <v>165</v>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23941,7 +23537,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -23987,7 +23583,6 @@
       <c r="G406" t="n">
         <v>165</v>
       </c>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23998,7 +23593,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -24044,7 +23639,6 @@
       <c r="G407" t="n">
         <v>165</v>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24055,7 +23649,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -24101,7 +23695,6 @@
       <c r="G408" t="n">
         <v>95</v>
       </c>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24112,7 +23705,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -24158,7 +23751,6 @@
       <c r="G409" t="n">
         <v>105</v>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24169,7 +23761,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -24215,7 +23807,6 @@
       <c r="G410" t="n">
         <v>95</v>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24226,7 +23817,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -24272,7 +23863,6 @@
       <c r="G411" t="n">
         <v>95</v>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24283,7 +23873,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -24329,7 +23919,6 @@
       <c r="G412" t="n">
         <v>115</v>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24340,7 +23929,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -24386,7 +23975,6 @@
       <c r="G413" t="n">
         <v>110</v>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24397,7 +23985,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -24443,7 +24031,6 @@
       <c r="G414" t="n">
         <v>110</v>
       </c>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24454,7 +24041,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -24500,7 +24087,6 @@
       <c r="G415" t="n">
         <v>110</v>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24511,7 +24097,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -24557,7 +24143,6 @@
       <c r="G416" t="n">
         <v>110</v>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24568,7 +24153,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -24614,7 +24199,6 @@
       <c r="G417" t="n">
         <v>95</v>
       </c>
-      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24625,7 +24209,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -24671,7 +24255,6 @@
       <c r="G418" t="n">
         <v>110</v>
       </c>
-      <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24682,7 +24265,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -24728,7 +24311,6 @@
       <c r="G419" t="n">
         <v>95</v>
       </c>
-      <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24739,7 +24321,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -24785,7 +24367,6 @@
       <c r="G420" t="n">
         <v>95</v>
       </c>
-      <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24796,7 +24377,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -24842,7 +24423,6 @@
       <c r="G421" t="n">
         <v>95</v>
       </c>
-      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24853,7 +24433,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -24899,7 +24479,6 @@
       <c r="G422" t="n">
         <v>95</v>
       </c>
-      <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24910,7 +24489,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -24956,7 +24535,6 @@
       <c r="G423" t="n">
         <v>95</v>
       </c>
-      <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24967,7 +24545,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -25013,7 +24591,6 @@
       <c r="G424" t="n">
         <v>95</v>
       </c>
-      <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25024,7 +24601,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -25070,7 +24647,6 @@
       <c r="G425" t="n">
         <v>110</v>
       </c>
-      <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25081,7 +24657,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -25127,7 +24703,6 @@
       <c r="G426" t="n">
         <v>95</v>
       </c>
-      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25138,7 +24713,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -25184,7 +24759,6 @@
       <c r="G427" t="n">
         <v>95</v>
       </c>
-      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25195,7 +24769,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -25241,7 +24815,6 @@
       <c r="G428" t="n">
         <v>95</v>
       </c>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25252,7 +24825,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -25298,7 +24871,6 @@
       <c r="G429" t="n">
         <v>185</v>
       </c>
-      <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25309,7 +24881,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -25355,7 +24927,6 @@
       <c r="G430" t="n">
         <v>110</v>
       </c>
-      <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25366,7 +24937,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -25412,7 +24983,6 @@
       <c r="G431" t="n">
         <v>110</v>
       </c>
-      <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25423,7 +24993,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -25469,7 +25039,6 @@
       <c r="G432" t="n">
         <v>110</v>
       </c>
-      <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25480,7 +25049,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -25526,7 +25095,6 @@
       <c r="G433" t="n">
         <v>185</v>
       </c>
-      <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25537,7 +25105,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -25559,7 +25127,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -25583,7 +25151,6 @@
       <c r="G434" t="n">
         <v>250</v>
       </c>
-      <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25594,7 +25161,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -25616,7 +25183,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -25640,7 +25207,6 @@
       <c r="G435" t="n">
         <v>180</v>
       </c>
-      <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25651,7 +25217,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -25673,7 +25239,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -25697,7 +25263,6 @@
       <c r="G436" t="n">
         <v>180</v>
       </c>
-      <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25708,7 +25273,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -25730,7 +25295,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -25754,7 +25319,6 @@
       <c r="G437" t="n">
         <v>180</v>
       </c>
-      <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25765,7 +25329,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -25787,7 +25351,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -25811,7 +25375,6 @@
       <c r="G438" t="n">
         <v>180</v>
       </c>
-      <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25822,7 +25385,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -25868,7 +25431,6 @@
       <c r="G439" t="n">
         <v>110</v>
       </c>
-      <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25879,7 +25441,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -25925,7 +25487,6 @@
       <c r="G440" t="n">
         <v>165</v>
       </c>
-      <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25936,7 +25497,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -25982,7 +25543,6 @@
       <c r="G441" t="n">
         <v>165</v>
       </c>
-      <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25993,7 +25553,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -26039,7 +25599,6 @@
       <c r="G442" t="n">
         <v>120</v>
       </c>
-      <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26050,7 +25609,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -26096,7 +25655,6 @@
       <c r="G443" t="n">
         <v>120</v>
       </c>
-      <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26107,7 +25665,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -26153,7 +25711,6 @@
       <c r="G444" t="n">
         <v>120</v>
       </c>
-      <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26164,7 +25721,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -26210,7 +25767,6 @@
       <c r="G445" t="n">
         <v>120</v>
       </c>
-      <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26221,7 +25777,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -26267,7 +25823,6 @@
       <c r="G446" t="n">
         <v>120</v>
       </c>
-      <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26278,7 +25833,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>Delivery 4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
